--- a/artfynd/A 21101-2023 artfynd.xlsx
+++ b/artfynd/A 21101-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21101-2023 artfynd.xlsx
+++ b/artfynd/A 21101-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62451520</v>
+        <v>112326609</v>
       </c>
       <c r="B2" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>3295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N om Stora Bugärde, Vg</t>
+          <t>Kärretvägen, Stora Bugärde, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345205.9298172994</v>
+        <v>345297</v>
       </c>
       <c r="R2" t="n">
-        <v>6394155.871631613</v>
+        <v>6394202</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,21 +757,519 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120716849</v>
+      </c>
+      <c r="B3" t="n">
+        <v>89080</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4373</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sprödvaxing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hygrocybe ceracea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Wulfen) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kärretvägen, Stora Bugärde, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>345297</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6394202</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Björketorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120716968</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89081</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulvaxing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kärretvägen, Stora Bugärde, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>345297</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6394202</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björketorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120718397</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89029</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kärretvägen, Stora Bugärde, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>345297</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6394202</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Björketorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>62451520</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N om Stora Bugärde, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>345206</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6394156</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Björketorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Lilian Karlsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Via Lilian Karlsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120716836</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kärretvägen, Stora Bugärde, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>345297</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6394202</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björketorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emma Nevander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21101-2023 artfynd.xlsx
+++ b/artfynd/A 21101-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112326609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716968</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120718397</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62451520</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,8 +1300,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120716836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>